--- a/lecture_slides/11_chapter_multiple_regression/data/autoparts_regression.xlsx
+++ b/lecture_slides/11_chapter_multiple_regression/data/autoparts_regression.xlsx
@@ -13,7 +13,6 @@
     <sheet name="VIF" sheetId="4" r:id="rId4"/>
     <sheet name="Model_Comparison" sheetId="5" r:id="rId5"/>
     <sheet name="Prediction" sheetId="6" r:id="rId6"/>
-    <sheet name="Butler_Anchor" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -368,27 +367,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>sales2012_k</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>population_3mi</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>income_3mi</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>yelp_rating</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>endcap</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sales2012_k</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>population_3mi</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>income_3mi</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>yelp_rating</t>
         </is>
       </c>
     </row>
@@ -397,19 +396,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>1651</v>
       </c>
       <c r="C2">
-        <v>1651</v>
+        <v>15432</v>
       </c>
       <c r="D2">
-        <v>15432</v>
+        <v>47644</v>
       </c>
       <c r="E2">
-        <v>47644</v>
+        <v>1.5</v>
       </c>
       <c r="F2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -417,19 +416,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3517</v>
       </c>
       <c r="C3">
-        <v>3517</v>
+        <v>51425</v>
       </c>
       <c r="D3">
-        <v>51425</v>
+        <v>31273</v>
       </c>
       <c r="E3">
-        <v>31273</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -437,19 +436,19 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3431</v>
       </c>
       <c r="C4">
-        <v>3431</v>
+        <v>54496</v>
       </c>
       <c r="D4">
-        <v>54496</v>
+        <v>67161</v>
       </c>
       <c r="E4">
-        <v>67161</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -457,16 +456,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>1328</v>
       </c>
       <c r="C5">
-        <v>1328</v>
+        <v>63234</v>
       </c>
       <c r="D5">
-        <v>63234</v>
+        <v>47911</v>
       </c>
       <c r="E5">
-        <v>47911</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -477,19 +476,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4677</v>
       </c>
       <c r="C6">
-        <v>4677</v>
+        <v>64222</v>
       </c>
       <c r="D6">
-        <v>64222</v>
+        <v>49429</v>
       </c>
       <c r="E6">
-        <v>49429</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -497,19 +496,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4699</v>
       </c>
       <c r="C7">
-        <v>4699</v>
+        <v>76547</v>
       </c>
       <c r="D7">
-        <v>76547</v>
+        <v>91781</v>
       </c>
       <c r="E7">
-        <v>91781</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -517,19 +516,19 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3704</v>
       </c>
       <c r="C8">
-        <v>3704</v>
+        <v>81091</v>
       </c>
       <c r="D8">
-        <v>81091</v>
+        <v>45834</v>
       </c>
       <c r="E8">
-        <v>45834</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -537,19 +536,19 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3907</v>
       </c>
       <c r="C9">
-        <v>3907</v>
+        <v>81495</v>
       </c>
       <c r="D9">
-        <v>81495</v>
+        <v>61567</v>
       </c>
       <c r="E9">
-        <v>61567</v>
+        <v>4.5</v>
       </c>
       <c r="F9">
-        <v>4.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -557,19 +556,19 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2441</v>
       </c>
       <c r="C10">
-        <v>2441</v>
+        <v>99660</v>
       </c>
       <c r="D10">
-        <v>99660</v>
+        <v>54657</v>
       </c>
       <c r="E10">
-        <v>54657</v>
+        <v>2.5</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -577,19 +576,19 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2550</v>
       </c>
       <c r="C11">
-        <v>2550</v>
+        <v>102122</v>
       </c>
       <c r="D11">
-        <v>102122</v>
+        <v>53474</v>
       </c>
       <c r="E11">
-        <v>53474</v>
+        <v>2.5</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -597,19 +596,19 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3887</v>
       </c>
       <c r="C12">
-        <v>3887</v>
+        <v>111246</v>
       </c>
       <c r="D12">
-        <v>111246</v>
+        <v>61989</v>
       </c>
       <c r="E12">
-        <v>61989</v>
+        <v>4.5</v>
       </c>
       <c r="F12">
-        <v>4.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -617,19 +616,19 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>5112</v>
       </c>
       <c r="C13">
-        <v>5112</v>
+        <v>116345</v>
       </c>
       <c r="D13">
-        <v>116345</v>
+        <v>56149</v>
       </c>
       <c r="E13">
-        <v>56149</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -637,19 +636,19 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>4677</v>
       </c>
       <c r="C14">
-        <v>4677</v>
+        <v>118329</v>
       </c>
       <c r="D14">
-        <v>118329</v>
+        <v>58673</v>
       </c>
       <c r="E14">
-        <v>58673</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -657,19 +656,19 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2933</v>
       </c>
       <c r="C15">
-        <v>2933</v>
+        <v>120915</v>
       </c>
       <c r="D15">
-        <v>120915</v>
+        <v>26588</v>
       </c>
       <c r="E15">
-        <v>26588</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -677,19 +676,19 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>4733</v>
       </c>
       <c r="C16">
-        <v>4733</v>
+        <v>133281</v>
       </c>
       <c r="D16">
-        <v>133281</v>
+        <v>68709</v>
       </c>
       <c r="E16">
-        <v>68709</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -697,19 +696,19 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>4607</v>
       </c>
       <c r="C17">
-        <v>4607</v>
+        <v>135325</v>
       </c>
       <c r="D17">
-        <v>135325</v>
+        <v>48502</v>
       </c>
       <c r="E17">
-        <v>48502</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -717,19 +716,19 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3375</v>
       </c>
       <c r="C18">
-        <v>3375</v>
+        <v>150982</v>
       </c>
       <c r="D18">
-        <v>150982</v>
+        <v>33792</v>
       </c>
       <c r="E18">
-        <v>33792</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -737,19 +736,19 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>1764</v>
       </c>
       <c r="C19">
-        <v>1764</v>
+        <v>182381</v>
       </c>
       <c r="D19">
-        <v>182381</v>
+        <v>35875</v>
       </c>
       <c r="E19">
-        <v>35875</v>
+        <v>1.5</v>
       </c>
       <c r="F19">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -757,19 +756,19 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>4360</v>
       </c>
       <c r="C20">
-        <v>4360</v>
+        <v>387887</v>
       </c>
       <c r="D20">
-        <v>387887</v>
+        <v>39480</v>
       </c>
       <c r="E20">
-        <v>39480</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -777,19 +776,19 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3444</v>
       </c>
       <c r="C21">
-        <v>3444</v>
+        <v>389167</v>
       </c>
       <c r="D21">
-        <v>389167</v>
+        <v>38821</v>
       </c>
       <c r="E21">
-        <v>38821</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -797,19 +796,19 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2285</v>
       </c>
       <c r="C22">
-        <v>2285</v>
+        <v>396904</v>
       </c>
       <c r="D22">
-        <v>396904</v>
+        <v>38957</v>
       </c>
       <c r="E22">
-        <v>38957</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -817,19 +816,19 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2734</v>
       </c>
       <c r="C23">
-        <v>2734</v>
+        <v>459473</v>
       </c>
       <c r="D23">
-        <v>459473</v>
+        <v>47320</v>
       </c>
       <c r="E23">
-        <v>47320</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -837,19 +836,19 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2496</v>
       </c>
       <c r="C24">
-        <v>2496</v>
+        <v>527877</v>
       </c>
       <c r="D24">
-        <v>527877</v>
+        <v>51200</v>
       </c>
       <c r="E24">
-        <v>51200</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -857,19 +856,19 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2631</v>
       </c>
       <c r="C25">
-        <v>2631</v>
+        <v>27486</v>
       </c>
       <c r="D25">
-        <v>27486</v>
+        <v>110148</v>
       </c>
       <c r="E25">
-        <v>110148</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -877,19 +876,19 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2165</v>
       </c>
       <c r="C26">
-        <v>2165</v>
+        <v>35436</v>
       </c>
       <c r="D26">
-        <v>35436</v>
+        <v>64938</v>
       </c>
       <c r="E26">
-        <v>64938</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -897,19 +896,19 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2869</v>
       </c>
       <c r="C27">
-        <v>2869</v>
+        <v>36788</v>
       </c>
       <c r="D27">
-        <v>36788</v>
+        <v>78608</v>
       </c>
       <c r="E27">
-        <v>78608</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -917,19 +916,19 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1926</v>
       </c>
       <c r="C28">
-        <v>1926</v>
+        <v>65415</v>
       </c>
       <c r="D28">
-        <v>65415</v>
+        <v>50281</v>
       </c>
       <c r="E28">
-        <v>50281</v>
+        <v>2.5</v>
       </c>
       <c r="F28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -937,19 +936,19 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>3291</v>
       </c>
       <c r="C29">
-        <v>3291</v>
+        <v>66395</v>
       </c>
       <c r="D29">
-        <v>66395</v>
+        <v>82936</v>
       </c>
       <c r="E29">
-        <v>82936</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -957,19 +956,19 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2302</v>
       </c>
       <c r="C30">
-        <v>2302</v>
+        <v>80210</v>
       </c>
       <c r="D30">
-        <v>80210</v>
+        <v>58287</v>
       </c>
       <c r="E30">
-        <v>58287</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -977,19 +976,19 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1913</v>
       </c>
       <c r="C31">
-        <v>1913</v>
+        <v>81438</v>
       </c>
       <c r="D31">
-        <v>81438</v>
+        <v>65130</v>
       </c>
       <c r="E31">
-        <v>65130</v>
+        <v>2.5</v>
       </c>
       <c r="F31">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -997,19 +996,19 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1681</v>
       </c>
       <c r="C32">
-        <v>1681</v>
+        <v>105833</v>
       </c>
       <c r="D32">
-        <v>105833</v>
+        <v>88587</v>
       </c>
       <c r="E32">
-        <v>88587</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1017,19 +1016,19 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="C33">
-        <v>1272</v>
+        <v>109139</v>
       </c>
       <c r="D33">
-        <v>109139</v>
+        <v>106508</v>
       </c>
       <c r="E33">
-        <v>106508</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1037,19 +1036,19 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2128</v>
       </c>
       <c r="C34">
-        <v>2128</v>
+        <v>110247</v>
       </c>
       <c r="D34">
-        <v>110247</v>
+        <v>73393</v>
       </c>
       <c r="E34">
-        <v>73393</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1057,19 +1056,19 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2362</v>
       </c>
       <c r="C35">
-        <v>2362</v>
+        <v>115501</v>
       </c>
       <c r="D35">
-        <v>115501</v>
+        <v>66667</v>
       </c>
       <c r="E35">
-        <v>66667</v>
+        <v>3.5</v>
       </c>
       <c r="F35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1077,19 +1076,19 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2069</v>
       </c>
       <c r="C36">
-        <v>2069</v>
+        <v>121059</v>
       </c>
       <c r="D36">
-        <v>121059</v>
+        <v>56754</v>
       </c>
       <c r="E36">
-        <v>56754</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1097,19 +1096,19 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="C37">
-        <v>1059</v>
+        <v>125624</v>
       </c>
       <c r="D37">
-        <v>125624</v>
+        <v>60894</v>
       </c>
       <c r="E37">
-        <v>60894</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1117,19 +1116,19 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1691</v>
       </c>
       <c r="C38">
-        <v>1691</v>
+        <v>127477</v>
       </c>
       <c r="D38">
-        <v>127477</v>
+        <v>73027</v>
       </c>
       <c r="E38">
-        <v>73027</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1137,19 +1136,19 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1399</v>
       </c>
       <c r="C39">
-        <v>1399</v>
+        <v>156559</v>
       </c>
       <c r="D39">
-        <v>156559</v>
+        <v>63554</v>
       </c>
       <c r="E39">
-        <v>63554</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1157,19 +1156,19 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1695</v>
       </c>
       <c r="C40">
-        <v>1695</v>
+        <v>163039</v>
       </c>
       <c r="D40">
-        <v>163039</v>
+        <v>36416</v>
       </c>
       <c r="E40">
-        <v>36416</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1177,19 +1176,19 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1502</v>
       </c>
       <c r="C41">
-        <v>1502</v>
+        <v>171086</v>
       </c>
       <c r="D41">
-        <v>171086</v>
+        <v>63085</v>
       </c>
       <c r="E41">
-        <v>63085</v>
+        <v>1.5</v>
       </c>
       <c r="F41">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1197,19 +1196,19 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2148</v>
       </c>
       <c r="C42">
-        <v>2148</v>
+        <v>192373</v>
       </c>
       <c r="D42">
-        <v>192373</v>
+        <v>44851</v>
       </c>
       <c r="E42">
-        <v>44851</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1217,19 +1216,19 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2033</v>
       </c>
       <c r="C43">
-        <v>2033</v>
+        <v>193961</v>
       </c>
       <c r="D43">
-        <v>193961</v>
+        <v>69780</v>
       </c>
       <c r="E43">
-        <v>69780</v>
+        <v>2.5</v>
       </c>
       <c r="F43">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1237,19 +1236,19 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1460</v>
       </c>
       <c r="C44">
-        <v>1460</v>
+        <v>250989</v>
       </c>
       <c r="D44">
-        <v>250989</v>
+        <v>60684</v>
       </c>
       <c r="E44">
-        <v>60684</v>
+        <v>1.5</v>
       </c>
       <c r="F44">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1257,19 +1256,19 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1690</v>
       </c>
       <c r="C45">
-        <v>1690</v>
+        <v>380860</v>
       </c>
       <c r="D45">
-        <v>380860</v>
+        <v>62821</v>
       </c>
       <c r="E45">
-        <v>62821</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1277,19 +1276,19 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2186</v>
       </c>
       <c r="C46">
-        <v>2186</v>
+        <v>386399</v>
       </c>
       <c r="D46">
-        <v>386399</v>
+        <v>44625</v>
       </c>
       <c r="E46">
-        <v>44625</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1873,176 +1872,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Assignment</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Miles_x1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Deliveries_x2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>TravelTime_y</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>50</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>50</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>80</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>75</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>65</v>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>90</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>90</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>